--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0016.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0016.xlsx
@@ -29109,7 +29109,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Bụng ta đau quá... chính xác là bị ngộ độc thực phẩm vì lỡ ăn nhầm loại thảo dược.</t>
+          <t>Bụng tao đau quá... chính xác là bị ngộ độc thực phẩm vì lỡ ăn nhầm loại thảo dược.</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Tớ đọc được một giai thoại trong *Hồng Trấn Ký Sự* về một chàng trai trẻ cách đây vài trăm năm, cậu ta phát hiện ra mận Pavo có tác dụng tăng cường trí nhớ tạm thời.</t>
+          <t>Tớ đọc được một giai thoại trong *Hongzhen Ký Sự* về một chàng trai trẻ cách đây vài trăm năm, cậu ta phát hiện ra mận Pavo có tác dụng tăng cường trí nhớ tạm thời.</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Ta đồng ý là câu chuyện có thể chỉ là hư cấu. Nhưng biết đâu đằng sau đó vẫn có chút sự thật.</t>
+          <t>Tao đồng ý là câu chuyện có thể chỉ là hư cấu. Nhưng biết đâu đằng sau đó vẫn có chút sự thật.</t>
         </is>
       </c>
     </row>
